--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512461_ELIMINGRA14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512461_ELIMINGRA14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.9046</v>
+        <v>10.0201</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6004</v>
+        <v>8.4701</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3042</v>
+        <v>1.5501</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1171</v>
+        <v>6.1856</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9402</v>
+        <v>1.9351</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1769</v>
+        <v>4.2505</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2138</v>
+        <v>6.5313</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4068</v>
+        <v>1.5704</v>
       </c>
       <c r="L2" t="n">
-        <v>4.8069</v>
+        <v>4.9609</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.3458</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5334</v>
+        <v>0.3647</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.63</v>
+        <v>-0.7104</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7274</v>
+        <v>1.7761</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8671</v>
+        <v>1.3798</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.3964</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4249</v>
+        <v>5.1084</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9318</v>
+        <v>4.9407</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4931</v>
+        <v>0.1677</v>
       </c>
       <c r="G3" t="n">
-        <v>8.0703</v>
+        <v>8.1717</v>
       </c>
       <c r="H3" t="n">
-        <v>6.9962</v>
+        <v>7.1508</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0741</v>
+        <v>1.0209</v>
       </c>
       <c r="J3" t="n">
-        <v>6.9235</v>
+        <v>7.1991</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6835</v>
+        <v>6.956</v>
       </c>
       <c r="L3" t="n">
-        <v>0.24</v>
+        <v>0.2432</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1469</v>
+        <v>0.9726</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3127</v>
+        <v>0.1949</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1756</v>
+        <v>1.6562</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8299</v>
+        <v>1.4084</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3457</v>
+        <v>0.2478</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6202</v>
+        <v>-1.6037</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1795</v>
+        <v>0.2279</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3804</v>
+        <v>4.2293</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6582</v>
+        <v>1.789</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7222</v>
+        <v>2.4402</v>
       </c>
       <c r="G4" t="n">
-        <v>3.771</v>
+        <v>3.7977</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2306</v>
+        <v>2.2774</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5404</v>
+        <v>1.5203</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6451</v>
+        <v>1.7739</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9252</v>
+        <v>1.0444</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7199</v>
+        <v>0.7295</v>
       </c>
       <c r="M4" t="n">
-        <v>2.1259</v>
+        <v>2.0238</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3055</v>
+        <v>1.233</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8205</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6894</v>
+        <v>0.5094</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4335</v>
+        <v>0.3978</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2559</v>
+        <v>0.1117</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3063</v>
+        <v>4.1606</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09080000000000001</v>
+        <v>1.7945</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3971</v>
+        <v>2.3661</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0249</v>
+        <v>4.0104</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4026</v>
+        <v>2.3846</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6222</v>
+        <v>1.6258</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9286</v>
+        <v>3.1285</v>
       </c>
       <c r="K5" t="n">
-        <v>2.283</v>
+        <v>2.4068</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6456</v>
+        <v>0.7217</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0963</v>
+        <v>0.8818</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1197</v>
+        <v>-0.0222</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9766</v>
+        <v>0.9041</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.6007</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9175</v>
+        <v>0.8502</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8179</v>
+        <v>0.7291</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09959999999999999</v>
+        <v>0.1211</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7545</v>
+        <v>1.4927</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2331</v>
+        <v>-0.238</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9875</v>
+        <v>1.7307</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9965</v>
+        <v>1.9404</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5759</v>
+        <v>1.5548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2634</v>
+        <v>1.3494</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4635</v>
+        <v>0.5389</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8105</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7331</v>
+        <v>0.591</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1125</v>
+        <v>1.0159</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3794</v>
+        <v>-0.4249</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6188</v>
+        <v>1.3371</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3049</v>
+        <v>1.0863</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3139</v>
+        <v>0.2508</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0534</v>
+        <v>1.0675</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8045</v>
+        <v>-0.3875</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8579</v>
+        <v>1.455</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9507</v>
+        <v>0.9755</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4088</v>
+        <v>-2.4287</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3595</v>
+        <v>3.4042</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1686</v>
+        <v>-0.0339</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.572</v>
+        <v>-2.5143</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4035</v>
+        <v>2.4805</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1193</v>
+        <v>1.0094</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1633</v>
+        <v>0.0856</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9237</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9026</v>
+        <v>0.8973</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1046</v>
+        <v>0.3406</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7981</v>
+        <v>0.5567</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>T. ALVES DE SOUZA SILVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1767</v>
+        <v>-0.0236</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1823</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09760000000000001</v>
+        <v>-0.2059</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3851</v>
+        <v>0.634</v>
       </c>
       <c r="H8" t="n">
-        <v>0.446</v>
+        <v>1.0458</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.4118</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2746</v>
+        <v>0.9853</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8688</v>
+        <v>0.9853</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5942</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6597</v>
+        <v>-0.3513</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4227</v>
+        <v>0.0605</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2369</v>
+        <v>-0.4118</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7616</v>
+        <v>0.1214</v>
       </c>
       <c r="T8" t="n">
-        <v>1.145</v>
+        <v>0.1707</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6166</v>
+        <v>-0.0494</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3401</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. ALVES DE SOUZA SILVA</t>
+          <t>J. FERRANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1432</v>
+        <v>-0.0509</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0339</v>
+        <v>0.2323</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1094</v>
+        <v>-0.2832</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6379</v>
+        <v>-0.2897</v>
       </c>
       <c r="H9" t="n">
-        <v>1.031</v>
+        <v>0.1221</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9597</v>
+        <v>0.0616</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9597</v>
+        <v>0.0616</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3218</v>
+        <v>-0.3513</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0191</v>
+        <v>0.0441</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0067</v>
+        <v>0.1707</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0124</v>
+        <v>-0.1267</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FERRANDEZ FERNANDEZ</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2683</v>
+        <v>-0.2362</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0667</v>
+        <v>0.1055</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.335</v>
+        <v>-0.3417</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2618</v>
+        <v>-0.3374</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1312</v>
+        <v>0.4958</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3931</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06</v>
+        <v>0.515</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06</v>
+        <v>1.0496</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.5346</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3218</v>
+        <v>-0.8524</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0713</v>
+        <v>-0.5538</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3931</v>
+        <v>-0.2986</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2065</v>
+        <v>1.3223</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0067</v>
+        <v>0.8953</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2132</v>
+        <v>0.4271</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4692</v>
+        <v>-0.2611</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0892</v>
+        <v>-0.9571</v>
       </c>
       <c r="F11" t="n">
-        <v>0.62</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3181</v>
+        <v>0.2945</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5824</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2781</v>
+        <v>0.254</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1872</v>
+        <v>0.0286</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1289</v>
+        <v>-0.024</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0583</v>
+        <v>0.0526</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3627</v>
+        <v>-0.6189</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.183</v>
+        <v>-0.7078</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1797</v>
+        <v>0.089</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7099</v>
+        <v>0.6343</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0305</v>
+        <v>-0.0755</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7405</v>
+        <v>0.7098</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2618</v>
+        <v>0.2908</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4581</v>
+        <v>-0.4387</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7199</v>
+        <v>0.7295</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4481</v>
+        <v>0.3436</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4275</v>
+        <v>0.3632</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0206</v>
+        <v>-0.0197</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6131</v>
+        <v>0.2473</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4445</v>
+        <v>-0.0249</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1686</v>
+        <v>0.2722</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6837</v>
+        <v>-1.2834</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0134</v>
+        <v>0.359</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6703</v>
+        <v>-1.6424</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7484</v>
+        <v>-1.7926</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.6579</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1198</v>
+        <v>-1.1347</v>
       </c>
       <c r="J13" t="n">
-        <v>0.18</v>
+        <v>0.1837</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1</v>
+        <v>0.1026</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9283</v>
+        <v>-1.9763</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7285</v>
+        <v>-0.7605</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2158</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1354</v>
+        <v>0.3145</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1934</v>
+        <v>0.1754</v>
       </c>
       <c r="U13" t="n">
-        <v>0.058</v>
+        <v>0.1391</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.0737</v>
+        <v>23.6045</v>
       </c>
       <c r="E14" t="n">
-        <v>11.8884</v>
+        <v>15.583</v>
       </c>
       <c r="F14" t="n">
-        <v>10.1852</v>
+        <v>8.021700000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>24.2011</v>
+        <v>24.2244</v>
       </c>
       <c r="H14" t="n">
-        <v>13.4216</v>
+        <v>13.5267</v>
       </c>
       <c r="I14" t="n">
-        <v>10.7794</v>
+        <v>10.6977</v>
       </c>
       <c r="J14" t="n">
-        <v>20.5819</v>
+        <v>22.02520000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>10.7204</v>
+        <v>11.7626</v>
       </c>
       <c r="L14" t="n">
-        <v>9.861499999999998</v>
+        <v>10.2628</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6195</v>
+        <v>2.1991</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7017</v>
+        <v>1.7642</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9180999999999997</v>
+        <v>0.4348999999999998</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.002199999999998</v>
+        <v>-7.7895</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0048</v>
+        <v>-16.5526</v>
       </c>
       <c r="R14" t="n">
-        <v>9.002599999999999</v>
+        <v>8.763</v>
       </c>
       <c r="S14" t="n">
-        <v>7.8348</v>
+        <v>9.1045</v>
       </c>
       <c r="T14" t="n">
-        <v>5.113700000000001</v>
+        <v>6.7052</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7213</v>
+        <v>2.3994</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.9603</v>
+        <v>-1.9347</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1979</v>
+        <v>3.4054</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.1582</v>
+        <v>-5.34</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0502</v>
+        <v>2.6634</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2754</v>
+        <v>5.5239</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2251</v>
+        <v>-2.8605</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3021</v>
+        <v>0.306</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8859</v>
+        <v>-0.9473</v>
       </c>
       <c r="I15" t="n">
-        <v>1.188</v>
+        <v>1.2534</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7105</v>
+        <v>3.9309</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3432</v>
+        <v>1.442</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3673</v>
+        <v>2.4888</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.4084</v>
+        <v>-3.6249</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.2291</v>
+        <v>-2.3894</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1793</v>
+        <v>-1.2355</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1726</v>
+        <v>-0.4963</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3651</v>
+        <v>0.372</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5377</v>
+        <v>-0.8683</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9201</v>
+        <v>0.9063</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2796</v>
+        <v>-0.3147</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7536</v>
+        <v>0.8598</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0177</v>
+        <v>0.1279</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7359</v>
+        <v>0.7319</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3537</v>
+        <v>0.3242</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0026</v>
+        <v>-0.0226</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3512</v>
+        <v>0.3469</v>
       </c>
       <c r="J16" t="n">
-        <v>0.14</v>
+        <v>0.1426</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06</v>
+        <v>0.0616</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2138</v>
+        <v>0.1816</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0574</v>
+        <v>-0.0842</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0002</v>
+        <v>0.1461</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1222</v>
+        <v>-0.0148</v>
       </c>
       <c r="U16" t="n">
-        <v>0.122</v>
+        <v>0.1608</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4476</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7681</v>
+        <v>1.3619</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2157</v>
+        <v>-1.8957</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3053</v>
+        <v>-0.2369</v>
       </c>
       <c r="H17" t="n">
-        <v>2.468</v>
+        <v>2.5463</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7733</v>
+        <v>-2.7832</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0319</v>
+        <v>3.3222</v>
       </c>
       <c r="K17" t="n">
-        <v>4.226</v>
+        <v>4.4646</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1941</v>
+        <v>-1.1425</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.3372</v>
+        <v>-3.5591</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.758</v>
+        <v>-1.9183</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5792</v>
+        <v>-1.6407</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0384</v>
+        <v>-0.1848</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4421</v>
+        <v>-0.2935</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4805</v>
+        <v>0.1087</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4194</v>
+        <v>0.4721</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3793</v>
+        <v>1.449</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9598</v>
+        <v>-0.9768</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>M. MELGAR ZORITA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0408</v>
+        <v>-0.598</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.796</v>
+        <v>-0.3807</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2448</v>
+        <v>-0.2173</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8667</v>
+        <v>-1.4992</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4668</v>
+        <v>0.0974</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3999</v>
+        <v>-1.5966</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3381</v>
+        <v>0.3863</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3381</v>
+        <v>1.0263</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.6401</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5286</v>
+        <v>-1.8854</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1287</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3999</v>
+        <v>-0.9565</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2001</v>
+        <v>2.1421</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4001</v>
+        <v>2.1421</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3741</v>
+        <v>-0.9614</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2578</v>
+        <v>-0.7669</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1163</v>
+        <v>-0.1945</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MELGAR ZORITA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.088</v>
+        <v>-0.8053</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8944</v>
+        <v>-0.5583</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1936</v>
+        <v>-0.247</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4415</v>
+        <v>-0.8655</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1563</v>
+        <v>-0.4603</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5979</v>
+        <v>-0.4053</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3236</v>
+        <v>-0.3156</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9997</v>
+        <v>-0.3156</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6761</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7651</v>
+        <v>-0.55</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8434</v>
+        <v>-0.1447</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9218</v>
+        <v>-0.4053</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2006</v>
+        <v>0.1947</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2006</v>
+        <v>0.3895</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5873</v>
+        <v>-0.1345</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.218</v>
+        <v>-0.048</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3693</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1442</v>
+        <v>-1.3642</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0495</v>
+        <v>-2.288</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9053</v>
+        <v>0.9237</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7332</v>
+        <v>-2.7521</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3978</v>
+        <v>-1.4035</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3354</v>
+        <v>-1.3487</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.954</v>
+        <v>-1.9114</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.276</v>
+        <v>-1.2469</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7792</v>
+        <v>-0.8407</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6574</v>
+        <v>-0.6842</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2318</v>
+        <v>-0.3579</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0955</v>
+        <v>-0.3765</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1363</v>
+        <v>0.0187</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1001</v>
+        <v>-1.4234</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2245</v>
+        <v>-0.1859</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3246</v>
+        <v>-1.2375</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4519</v>
+        <v>-3.9755</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2902</v>
+        <v>-5.1591</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1617</v>
+        <v>1.1836</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3199</v>
+        <v>-0.1204</v>
       </c>
       <c r="K21" t="n">
-        <v>0.16</v>
+        <v>-3.2172</v>
       </c>
       <c r="L21" t="n">
-        <v>0.16</v>
+        <v>3.0967</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7718</v>
+        <v>-3.8551</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4501</v>
+        <v>-1.942</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3217</v>
+        <v>-1.9131</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6005</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6005</v>
+        <v>2.7263</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7291</v>
+        <v>-0.9979</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0955</v>
+        <v>-0.5934</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.4045</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5196</v>
+        <v>2.9658</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5196</v>
+        <v>0.2958</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2652</v>
+        <v>-2.2108</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6667</v>
+        <v>0.0495</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5985</v>
+        <v>-2.2603</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0615</v>
+        <v>-2.5684</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.1851</v>
+        <v>-1.3686</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1236</v>
+        <v>-1.1997</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4738</v>
+        <v>0.3263</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.441</v>
+        <v>0.1642</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9672</v>
+        <v>0.1621</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.5877</v>
+        <v>-2.8947</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7442</v>
+        <v>-1.5329</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8435</v>
+        <v>-1.3618</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6002</v>
+        <v>1.5579</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2006</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8008</v>
+        <v>1.5579</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.7031</v>
+        <v>-0.6414</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5713</v>
+        <v>-0.2769</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1318</v>
+        <v>-0.3646</v>
       </c>
       <c r="V22" t="n">
-        <v>2.8993</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>2.579</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3203</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.0807</v>
+        <v>-7.7011</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1425</v>
+        <v>-5.8259</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9382</v>
+        <v>-1.8752</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.1736</v>
+        <v>-6.1823</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.9553</v>
+        <v>-3.9974</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2184</v>
+        <v>-2.1848</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.6222</v>
+        <v>-4.4784</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.1901</v>
+        <v>-3.1173</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4322</v>
+        <v>-1.3612</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5514</v>
+        <v>-1.7038</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7652</v>
+        <v>-0.8802</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7862</v>
+        <v>-0.8236</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.3209</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3199</v>
+        <v>-0.179</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4276</v>
+        <v>-0.1419</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5597</v>
+        <v>-1.5874</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5597</v>
+        <v>-1.5874</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.711</v>
+        <v>-8.2873</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.922</v>
+        <v>-5.8459</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.789</v>
+        <v>-2.4413</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.8232</v>
+        <v>-6.7747</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.8676</v>
+        <v>-2.8115</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.9556</v>
+        <v>-3.9632</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.7572</v>
+        <v>-3.4814</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2452</v>
+        <v>-1.026</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.512</v>
+        <v>-2.4554</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.066</v>
+        <v>-3.2932</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6224</v>
+        <v>-1.7854</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4436</v>
+        <v>-1.5078</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3278</v>
+        <v>-0.9515</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0358</v>
+        <v>-0.2224</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3636</v>
+        <v>-0.7291</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-22.0738</v>
+        <v>-19.4007</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.1854</v>
+        <v>-8.0215</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.8883</v>
+        <v>-11.3792</v>
       </c>
       <c r="G25" t="n">
-        <v>-24.2011</v>
+        <v>-24.2244</v>
       </c>
       <c r="H25" t="n">
-        <v>-13.4218</v>
+        <v>-13.5266</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.7794</v>
+        <v>-10.6976</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.619400000000001</v>
+        <v>-2.198899999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.7015</v>
+        <v>-1.7643</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9178999999999995</v>
+        <v>-0.4349999999999996</v>
       </c>
       <c r="M25" t="n">
-        <v>-20.5816</v>
+        <v>-22.0253</v>
       </c>
       <c r="N25" t="n">
-        <v>-10.7203</v>
+        <v>-11.7625</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.8614</v>
+        <v>-10.2627</v>
       </c>
       <c r="P25" t="n">
-        <v>8.0023</v>
+        <v>7.7896</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.0025</v>
+        <v>-8.763100000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0049</v>
+        <v>16.5528</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.835099999999999</v>
+        <v>-4.9005</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.7214</v>
+        <v>-2.3994</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.1137</v>
+        <v>-2.5012</v>
       </c>
       <c r="V25" t="n">
-        <v>1.9602</v>
+        <v>1.9346</v>
       </c>
       <c r="W25" t="n">
-        <v>5.1581</v>
+        <v>5.3401</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.1977</v>
+        <v>-3.4053</v>
       </c>
     </row>
   </sheetData>
